--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9257396368</v>
+        <v>46157.93115829315</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115829315</v>
+        <v>46157.93182062169</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93182062169</v>
+        <v>46157.93405240169</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405240169</v>
+        <v>46157.93723327808</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723327808</v>
+        <v>46158.28221143721</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221143721</v>
+        <v>46158.29701079007</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701079007</v>
+        <v>46158.29820818071</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820818071</v>
+        <v>46158.33392173985</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392173985</v>
+        <v>46158.36861943048</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Ладин- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861943048</v>
+        <v>46158.37292651278</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
